--- a/ARM Functions/Other Mechanics/Move Relearner Replaces Cafe.xlsx
+++ b/ARM Functions/Other Mechanics/Move Relearner Replaces Cafe.xlsx
@@ -1,23 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dropbox\ROM\3ds\USUM ARM research\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dropbox\ROM\3ds\USUM ARM research\Other Mechanics\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66FA90A5-6FE8-4BA0-B0AE-D0A3562CE339}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A268490D-029F-4E19-8201-629743B66318}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="33120" windowHeight="18120" xr2:uid="{FFF8744C-F0B4-428F-8CA7-718350CADE02}"/>
+    <workbookView xWindow="3360" yWindow="3360" windowWidth="24686" windowHeight="13149" activeTab="1" xr2:uid="{FFF8744C-F0B4-428F-8CA7-718350CADE02}"/>
   </bookViews>
   <sheets>
     <sheet name="Copy Output" sheetId="10" r:id="rId1"/>
     <sheet name="Edited main" sheetId="6" r:id="rId2"/>
-    <sheet name="original" sheetId="5" r:id="rId3"/>
+    <sheet name="Cafe Script IDs" sheetId="11" r:id="rId3"/>
+    <sheet name="original" sheetId="5" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029" iterate="1" iterateCount="5"/>
+  <calcPr calcId="191028" iterate="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="157">
   <si>
     <t>Address</t>
   </si>
@@ -61,18 +62,12 @@
     <t>Thing to paste starting there</t>
   </si>
   <si>
-    <t>pop {r2}</t>
-  </si>
-  <si>
     <t>cmp r0, r4</t>
   </si>
   <si>
     <t>040050E1</t>
   </si>
   <si>
-    <t>04209DE4</t>
-  </si>
-  <si>
     <t>00F020E3</t>
   </si>
   <si>
@@ -133,9 +128,6 @@
     <t>003418C4</t>
   </si>
   <si>
-    <t>push {r2}</t>
-  </si>
-  <si>
     <t>push {r4, r5, r6, r7, r8, sb, sl, fp, lr}</t>
   </si>
   <si>
@@ -172,54 +164,6 @@
     <t>0800D0E5</t>
   </si>
   <si>
-    <t>café id min</t>
-  </si>
-  <si>
-    <t>café id max</t>
-  </si>
-  <si>
-    <t>relearner id</t>
-  </si>
-  <si>
-    <t>B7140000</t>
-  </si>
-  <si>
-    <t>AA140000</t>
-  </si>
-  <si>
-    <t>7C150000</t>
-  </si>
-  <si>
-    <t>load café id min</t>
-  </si>
-  <si>
-    <t>cmp r1, r2</t>
-  </si>
-  <si>
-    <t>load café id max</t>
-  </si>
-  <si>
-    <t>04202DE5</t>
-  </si>
-  <si>
-    <t>020051E1</t>
-  </si>
-  <si>
-    <t>030000BA</t>
-  </si>
-  <si>
-    <t>000000CA</t>
-  </si>
-  <si>
-    <t>20209FE5</t>
-  </si>
-  <si>
-    <t>18209FE5</t>
-  </si>
-  <si>
-    <t>10109FE5</t>
-  </si>
-  <si>
     <t>Prevent too-high-level moves from appearing</t>
   </si>
   <si>
@@ -259,9 +203,6 @@
     <t>004B9F8C</t>
   </si>
   <si>
-    <t>59E205EB</t>
-  </si>
-  <si>
     <t>CF7F08EB</t>
   </si>
   <si>
@@ -289,9 +230,6 @@
     <t>UM code.bin</t>
   </si>
   <si>
-    <t>58E205EB</t>
-  </si>
-  <si>
     <t>push {r4, r5, r6, r7, r8, r9, r10, lr}</t>
   </si>
   <si>
@@ -331,30 +269,9 @@
     <t>01A0A0E1</t>
   </si>
   <si>
-    <t>37A6F5EB</t>
-  </si>
-  <si>
-    <t>351EFABA</t>
-  </si>
-  <si>
-    <t>F91DFAEA</t>
-  </si>
-  <si>
-    <t>361EFABA</t>
-  </si>
-  <si>
-    <t>FA1DFAEA</t>
-  </si>
-  <si>
     <t>F0472DE9</t>
   </si>
   <si>
-    <t>FCE105EA</t>
-  </si>
-  <si>
-    <t>FBE105EA</t>
-  </si>
-  <si>
     <t>Address US</t>
   </si>
   <si>
@@ -365,13 +282,241 @@
   </si>
   <si>
     <t>Length (bytes, hex)</t>
+  </si>
+  <si>
+    <t>5290</t>
+  </si>
+  <si>
+    <t>5291</t>
+  </si>
+  <si>
+    <t>5292</t>
+  </si>
+  <si>
+    <t>5293</t>
+  </si>
+  <si>
+    <t>5294</t>
+  </si>
+  <si>
+    <t>5295</t>
+  </si>
+  <si>
+    <t>5296</t>
+  </si>
+  <si>
+    <t>5297</t>
+  </si>
+  <si>
+    <t>5298</t>
+  </si>
+  <si>
+    <t>5299</t>
+  </si>
+  <si>
+    <t>5300</t>
+  </si>
+  <si>
+    <t>5301</t>
+  </si>
+  <si>
+    <t>5302</t>
+  </si>
+  <si>
+    <t>5303</t>
+  </si>
+  <si>
+    <t>5304</t>
+  </si>
+  <si>
+    <t>Pokemon Center</t>
+  </si>
+  <si>
+    <t>Route 1</t>
+  </si>
+  <si>
+    <t>Hau'oli City</t>
+  </si>
+  <si>
+    <t>Route 2</t>
+  </si>
+  <si>
+    <t>Heahea City</t>
+  </si>
+  <si>
+    <t>Royal Avenue</t>
+  </si>
+  <si>
+    <t>Route 8</t>
+  </si>
+  <si>
+    <t>Konikoni City</t>
+  </si>
+  <si>
+    <t>Malie City</t>
+  </si>
+  <si>
+    <t>Tapu Village</t>
+  </si>
+  <si>
+    <t>Seafolk Village</t>
+  </si>
+  <si>
+    <t>Paniola Town</t>
+  </si>
+  <si>
+    <t>Route 5</t>
+  </si>
+  <si>
+    <t>Mount Hokulani/Route 10</t>
+  </si>
+  <si>
+    <t>Mount Lanakila/Pokemon League</t>
+  </si>
+  <si>
+    <t>Route 16</t>
+  </si>
+  <si>
+    <t>Dec</t>
+  </si>
+  <si>
+    <t>Move Relearner</t>
+  </si>
+  <si>
+    <t>Super Training</t>
+  </si>
+  <si>
+    <t>Plan</t>
+  </si>
+  <si>
+    <t>Café</t>
+  </si>
+  <si>
+    <t>sub r2, r1, 0x1400</t>
+  </si>
+  <si>
+    <t>subs r2, r2, 0xAA</t>
+  </si>
+  <si>
+    <t>lowest PC now 0</t>
+  </si>
+  <si>
+    <t>Highest now E</t>
+  </si>
+  <si>
+    <t>cmp r2, 0xE</t>
+  </si>
+  <si>
+    <t>lsr r2, r2, #2</t>
+  </si>
+  <si>
+    <t>push {r2, r3, lr}</t>
+  </si>
+  <si>
+    <t>and r3, r2, 0x3</t>
+  </si>
+  <si>
+    <t>add r3, r2, r3</t>
+  </si>
+  <si>
+    <t>cmp r3, 0x3</t>
+  </si>
+  <si>
+    <t>subhs r3, r3, 0x3</t>
+  </si>
+  <si>
+    <t>take module 3</t>
+  </si>
+  <si>
+    <t>cmp r3, 0x1</t>
+  </si>
+  <si>
+    <t>7C151716</t>
+  </si>
+  <si>
+    <t>Relearner ID | Hyper Training ID</t>
+  </si>
+  <si>
+    <t>Hyper Training</t>
+  </si>
+  <si>
+    <t>0C402DE9</t>
+  </si>
+  <si>
+    <t>052B41E2</t>
+  </si>
+  <si>
+    <t>AA2052E2</t>
+  </si>
+  <si>
+    <t>090000BA</t>
+  </si>
+  <si>
+    <t>0E0052E3</t>
+  </si>
+  <si>
+    <t>0700008A</t>
+  </si>
+  <si>
+    <t>033002E2</t>
+  </si>
+  <si>
+    <t>2221A0E1</t>
+  </si>
+  <si>
+    <t>033082E0</t>
+  </si>
+  <si>
+    <t>030053E3</t>
+  </si>
+  <si>
+    <t>03304322</t>
+  </si>
+  <si>
+    <t>010053E3</t>
+  </si>
+  <si>
+    <t>B410DF31</t>
+  </si>
+  <si>
+    <t>B210DF81</t>
+  </si>
+  <si>
+    <t>0C80BDE8</t>
+  </si>
+  <si>
+    <t>331EFABA</t>
+  </si>
+  <si>
+    <t>F71DFAEA</t>
+  </si>
+  <si>
+    <t>FEE105EA</t>
+  </si>
+  <si>
+    <t>5BE205EB</t>
+  </si>
+  <si>
+    <t>34A6F5EB</t>
+  </si>
+  <si>
+    <t>FFE105EA</t>
+  </si>
+  <si>
+    <t>5CE205EB</t>
+  </si>
+  <si>
+    <t>321EFABA</t>
+  </si>
+  <si>
+    <t>F61DFAEA</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -393,6 +538,31 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Cascadia Code"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Cascadia Code"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Cascadia Code"/>
+      <family val="3"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -588,11 +758,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -617,7 +785,22 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -966,187 +1149,187 @@
   <dimension ref="A1:C16"/>
   <sheetFormatPr defaultRowHeight="14.15"/>
   <cols>
-    <col min="1" max="1" width="32.5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="39.2109375" customWidth="1"/>
-    <col min="3" max="3" width="23.2109375" customWidth="1"/>
-    <col min="4" max="5" width="11.92578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="32.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="39.140625" customWidth="1"/>
+    <col min="3" max="3" width="23.28515625" customWidth="1"/>
+    <col min="4" max="5" width="12" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="14.6" thickTop="1">
-      <c r="A1" s="17" t="s">
-        <v>81</v>
-      </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="19"/>
+      <c r="A1" s="30" t="s">
+        <v>61</v>
+      </c>
+      <c r="B1" s="31"/>
+      <c r="C1" s="32"/>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="11" t="s">
+      <c r="B2" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="12" t="s">
-        <v>108</v>
+      <c r="C2" s="10" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="5" t="str">
+      <c r="A3" s="3" t="str">
         <f>'Edited main'!A3</f>
         <v>0029A048</v>
       </c>
-      <c r="B3" s="6" t="str">
+      <c r="B3" s="4" t="str">
         <f>_xlfn.CONCAT('Edited main'!B3)</f>
         <v>CF7F08EB</v>
       </c>
-      <c r="C3" s="7" t="str">
+      <c r="C3" s="5" t="str">
         <f>DEC2HEX(LEN(B3)/2,3)</f>
         <v>004</v>
       </c>
     </row>
     <row r="4" spans="1:3">
-      <c r="A4" s="13" t="str">
+      <c r="A4" s="11" t="str">
         <f>'Edited main'!A9</f>
         <v>00341654</v>
       </c>
-      <c r="B4" s="15" t="str">
+      <c r="B4" s="13" t="str">
         <f>_xlfn.CONCAT('Edited main'!B9:B10)</f>
-        <v>F0472DE959E205EB</v>
-      </c>
-      <c r="C4" s="14" t="str">
+        <v>F0472DE95CE205EB</v>
+      </c>
+      <c r="C4" s="12" t="str">
         <f t="shared" ref="C4:C7" si="0">DEC2HEX(LEN(B4)/2,3)</f>
         <v>008</v>
       </c>
     </row>
     <row r="5" spans="1:3">
-      <c r="A5" s="13" t="str">
+      <c r="A5" s="11" t="str">
         <f>'Edited main'!A13</f>
         <v>003417D8</v>
       </c>
-      <c r="B5" s="15" t="str">
+      <c r="B5" s="13" t="str">
         <f>_xlfn.CONCAT('Edited main'!B13:B14)</f>
-        <v>FCE105EA00F020E3</v>
-      </c>
-      <c r="C5" s="14" t="str">
+        <v>FFE105EA00F020E3</v>
+      </c>
+      <c r="C5" s="12" t="str">
         <f t="shared" si="0"/>
         <v>008</v>
       </c>
     </row>
     <row r="6" spans="1:3">
-      <c r="A6" s="13" t="str">
+      <c r="A6" s="11" t="str">
         <f>'Edited main'!A17</f>
         <v>003418EC</v>
       </c>
-      <c r="B6" s="15" t="str">
+      <c r="B6" s="13" t="str">
         <f>_xlfn.CONCAT('Edited main'!B17)</f>
         <v>F087BDE8</v>
       </c>
-      <c r="C6" s="14" t="str">
+      <c r="C6" s="12" t="str">
         <f t="shared" si="0"/>
         <v>004</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="14.6" thickBot="1">
-      <c r="A7" s="8" t="str">
+      <c r="A7" s="6" t="str">
         <f>'Edited main'!A25</f>
         <v>004B9F8C</v>
       </c>
-      <c r="B7" s="9" t="str">
-        <f>_xlfn.CONCAT('Edited main'!B25:B64)</f>
-        <v>04202DE520209FE5020051E1030000BA18209FE5020051E1000000CA10109FE504209DE40CD04DE21EFF2FE1AA140000B71400007C15000001A0A0E10CD04DE21EFF2FE11F402DE90040A0E10A00A0E137A6F5EB040050E11F40BDE8351EFABA020050E3F91DFAEA</v>
-      </c>
-      <c r="C7" s="10" t="str">
+      <c r="B7" s="7" t="str">
+        <f>_xlfn.CONCAT('Edited main'!B25:B67)</f>
+        <v>0CD04DE20C402DE9052B41E2AA2052E2090000BA0E0052E30700008A033002E22221A0E1033082E0030053E303304322010053E3B410DF31B210DF810C80BDE87C15171601A0A0E10CD04DE21EFF2FE11F402DE90040A0E10A00A0E134A6F5EB040050E11F40BDE8321EFABA020050E3F61DFAEA</v>
+      </c>
+      <c r="C7" s="8" t="str">
         <f t="shared" si="0"/>
-        <v>068</v>
+        <v>074</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="15" thickTop="1" thickBot="1"/>
     <row r="9" spans="1:3" ht="14.6" thickTop="1">
-      <c r="A9" s="17" t="s">
-        <v>82</v>
-      </c>
-      <c r="B9" s="18"/>
-      <c r="C9" s="19"/>
+      <c r="A9" s="30" t="s">
+        <v>62</v>
+      </c>
+      <c r="B9" s="31"/>
+      <c r="C9" s="32"/>
     </row>
     <row r="10" spans="1:3">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B10" s="11" t="s">
+      <c r="B10" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="C10" s="12" t="s">
-        <v>108</v>
+      <c r="C10" s="10" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="11" spans="1:3">
-      <c r="A11" s="5" t="str">
+      <c r="A11" s="3" t="str">
         <f>'Edited main'!E3</f>
         <v>0029A048</v>
       </c>
-      <c r="B11" s="6" t="str">
+      <c r="B11" s="4" t="str">
         <f>_xlfn.CONCAT('Edited main'!F3)</f>
         <v>CF7F08EB</v>
       </c>
-      <c r="C11" s="7" t="str">
+      <c r="C11" s="5" t="str">
         <f>DEC2HEX(LEN(B11)/2,3)</f>
         <v>004</v>
       </c>
     </row>
     <row r="12" spans="1:3">
-      <c r="A12" s="13" t="str">
+      <c r="A12" s="11" t="str">
         <f>'Edited main'!E9</f>
         <v>00341658</v>
       </c>
-      <c r="B12" s="15" t="str">
+      <c r="B12" s="13" t="str">
         <f>_xlfn.CONCAT('Edited main'!F9:F10)</f>
-        <v>F0472DE958E205EB</v>
-      </c>
-      <c r="C12" s="14" t="str">
+        <v>F0472DE95BE205EB</v>
+      </c>
+      <c r="C12" s="12" t="str">
         <f t="shared" ref="C12:C15" si="1">DEC2HEX(LEN(B12)/2,3)</f>
         <v>008</v>
       </c>
     </row>
     <row r="13" spans="1:3">
-      <c r="A13" s="13" t="str">
+      <c r="A13" s="11" t="str">
         <f>'Edited main'!E13</f>
         <v>003417DC</v>
       </c>
-      <c r="B13" s="15" t="str">
+      <c r="B13" s="13" t="str">
         <f>_xlfn.CONCAT('Edited main'!F13:F14)</f>
-        <v>FBE105EA00F020E3</v>
-      </c>
-      <c r="C13" s="14" t="str">
+        <v>FEE105EA00F020E3</v>
+      </c>
+      <c r="C13" s="12" t="str">
         <f t="shared" si="1"/>
         <v>008</v>
       </c>
     </row>
     <row r="14" spans="1:3">
-      <c r="A14" s="13" t="str">
+      <c r="A14" s="11" t="str">
         <f>'Edited main'!E17</f>
         <v>003418F0</v>
       </c>
-      <c r="B14" s="15" t="str">
+      <c r="B14" s="13" t="str">
         <f>_xlfn.CONCAT('Edited main'!F17)</f>
         <v>F087BDE8</v>
       </c>
-      <c r="C14" s="14" t="str">
+      <c r="C14" s="12" t="str">
         <f t="shared" si="1"/>
         <v>004</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="14.6" thickBot="1">
-      <c r="A15" s="8" t="str">
+      <c r="A15" s="6" t="str">
         <f>'Edited main'!E25</f>
         <v>004B9F8C</v>
       </c>
-      <c r="B15" s="9" t="str">
-        <f>_xlfn.CONCAT('Edited main'!F25:F64)</f>
-        <v>04202DE520209FE5020051E1030000BA18209FE5020051E1000000CA10109FE504209DE40CD04DE21EFF2FE1AA140000B71400007C15000001A0A0E10CD04DE21EFF2FE11F402DE90040A0E10A00A0E137A6F5EB040050E11F40BDE8361EFABA020050E3FA1DFAEA</v>
-      </c>
-      <c r="C15" s="10" t="str">
+      <c r="B15" s="7" t="str">
+        <f>_xlfn.CONCAT('Edited main'!F25:F67)</f>
+        <v>0CD04DE20C402DE9052B41E2AA2052E2090000BA0E0052E30700008A033002E22221A0E1033082E0030053E303304322010053E3B410DF31B210DF810C80BDE87C15171601A0A0E10CD04DE21EFF2FE11F402DE90040A0E10A00A0E134A6F5EB040050E11F40BDE8331EFABA020050E3F71DFAEA</v>
+      </c>
+      <c r="C15" s="8" t="str">
         <f t="shared" si="1"/>
-        <v>068</v>
+        <v>074</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="14.6" thickTop="1"/>
@@ -1162,918 +1345,1022 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD17F403-0334-4F0F-BD62-1976F89E9C58}">
-  <dimension ref="A1:G54"/>
-  <sheetFormatPr defaultRowHeight="14.15"/>
+  <dimension ref="A1:G57"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15.9"/>
   <cols>
-    <col min="1" max="1" width="11.640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.35546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="47.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="27.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.35546875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.5703125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="17.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.7109375" style="25" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.42578125" style="25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="47.78515625" style="25" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="27.28515625" style="25" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10.0703125" style="25" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.42578125" style="25" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.5703125" style="25" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="17.2109375" style="25" bestFit="1" customWidth="1"/>
+    <col min="9" max="16384" width="9.140625" style="25"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="D1" s="4" t="s">
+      <c r="A1" s="24" t="s">
+        <v>77</v>
+      </c>
+      <c r="B1" s="24" t="s">
+        <v>78</v>
+      </c>
+      <c r="C1" s="24" t="s">
+        <v>79</v>
+      </c>
+      <c r="D1" s="24" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>75</v>
+      <c r="E1" s="24" t="s">
+        <v>57</v>
+      </c>
+      <c r="F1" s="24" t="s">
+        <v>56</v>
+      </c>
+      <c r="G1" s="24" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="B2" s="16"/>
-      <c r="C2" s="16"/>
-      <c r="D2" s="16"/>
-      <c r="E2" s="16"/>
-      <c r="F2" s="16"/>
-      <c r="G2" s="16"/>
+      <c r="A2" s="29" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" s="29"/>
+      <c r="C2" s="29"/>
+      <c r="D2" s="29"/>
+      <c r="E2" s="29"/>
+      <c r="F2" s="29"/>
+      <c r="G2" s="29"/>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" t="s">
-        <v>33</v>
-      </c>
-      <c r="B3" t="s">
-        <v>74</v>
-      </c>
-      <c r="C3" t="str">
+      <c r="A3" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="B3" s="25" t="s">
+        <v>54</v>
+      </c>
+      <c r="C3" s="25" t="str">
         <f>_xlfn.CONCAT("bl 0x",A25)</f>
         <v>bl 0x004B9F8C</v>
       </c>
-      <c r="E3" t="s">
-        <v>33</v>
-      </c>
-      <c r="F3" t="s">
-        <v>74</v>
-      </c>
-      <c r="G3" t="str">
+      <c r="E3" s="25" t="s">
+        <v>30</v>
+      </c>
+      <c r="F3" s="25" t="s">
+        <v>54</v>
+      </c>
+      <c r="G3" s="25" t="str">
         <f>_xlfn.CONCAT("bl 0x",E25)</f>
         <v>bl 0x004B9F8C</v>
       </c>
     </row>
     <row r="5" spans="1:7">
-      <c r="A5" s="16" t="s">
-        <v>21</v>
-      </c>
-      <c r="B5" s="16"/>
-      <c r="C5" s="16"/>
-      <c r="D5" s="16"/>
-      <c r="E5" s="16"/>
-      <c r="F5" s="16"/>
-      <c r="G5" s="16"/>
+      <c r="A5" s="29" t="s">
+        <v>19</v>
+      </c>
+      <c r="B5" s="29"/>
+      <c r="C5" s="29"/>
+      <c r="D5" s="29"/>
+      <c r="E5" s="29"/>
+      <c r="F5" s="29"/>
+      <c r="G5" s="29"/>
     </row>
     <row r="6" spans="1:7">
-      <c r="A6" t="s">
-        <v>29</v>
-      </c>
-      <c r="E6" t="s">
-        <v>29</v>
+      <c r="A6" s="25" t="s">
+        <v>27</v>
+      </c>
+      <c r="E6" s="25" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="8" spans="1:7">
-      <c r="A8" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="B8" s="16"/>
-      <c r="C8" s="16"/>
-      <c r="D8" s="16"/>
-      <c r="E8" s="16"/>
-      <c r="F8" s="16"/>
-      <c r="G8" s="16"/>
+      <c r="A8" s="29" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="29"/>
+      <c r="C8" s="29"/>
+      <c r="D8" s="29"/>
+      <c r="E8" s="29"/>
+      <c r="F8" s="29"/>
+      <c r="G8" s="29"/>
     </row>
     <row r="9" spans="1:7">
-      <c r="A9" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="B9" t="s">
-        <v>102</v>
-      </c>
-      <c r="C9" t="s">
-        <v>84</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="F9" t="s">
-        <v>102</v>
-      </c>
-      <c r="G9" t="s">
-        <v>84</v>
+      <c r="A9" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="25" t="s">
+        <v>76</v>
+      </c>
+      <c r="C9" s="25" t="s">
+        <v>63</v>
+      </c>
+      <c r="E9" s="26" t="s">
+        <v>58</v>
+      </c>
+      <c r="F9" s="25" t="s">
+        <v>76</v>
+      </c>
+      <c r="G9" s="25" t="s">
+        <v>63</v>
       </c>
     </row>
     <row r="10" spans="1:7">
-      <c r="A10" t="str">
+      <c r="A10" s="25" t="str">
         <f t="shared" ref="A10" si="0">DEC2HEX(HEX2DEC(A9)+4,8)</f>
         <v>00341658</v>
       </c>
-      <c r="B10" t="s">
-        <v>73</v>
-      </c>
-      <c r="C10" t="str">
-        <f>_xlfn.CONCAT("bl 0x",A41)</f>
-        <v>bl 0x004B9FC4</v>
-      </c>
-      <c r="E10" t="str">
+      <c r="B10" s="25" t="s">
+        <v>154</v>
+      </c>
+      <c r="C10" s="25" t="str">
+        <f>_xlfn.CONCAT("bl 0x",A44)</f>
+        <v>bl 0x004B9FD0</v>
+      </c>
+      <c r="E10" s="25" t="str">
         <f t="shared" ref="E10" si="1">DEC2HEX(HEX2DEC(E9)+4,8)</f>
         <v>0034165C</v>
       </c>
-      <c r="F10" t="s">
-        <v>83</v>
-      </c>
-      <c r="G10" t="str">
-        <f>_xlfn.CONCAT("bl 0x",E41)</f>
-        <v>bl 0x004B9FC4</v>
+      <c r="F10" s="25" t="s">
+        <v>151</v>
+      </c>
+      <c r="G10" s="25" t="str">
+        <f>_xlfn.CONCAT("bl 0x",E44)</f>
+        <v>bl 0x004B9FD0</v>
       </c>
     </row>
     <row r="12" spans="1:7">
-      <c r="A12" s="16" t="s">
-        <v>88</v>
-      </c>
-      <c r="B12" s="16"/>
-      <c r="C12" s="16"/>
-      <c r="D12" s="16"/>
-      <c r="E12" s="16"/>
-      <c r="F12" s="16"/>
-      <c r="G12" s="16"/>
+      <c r="A12" s="29" t="s">
+        <v>67</v>
+      </c>
+      <c r="B12" s="29"/>
+      <c r="C12" s="29"/>
+      <c r="D12" s="29"/>
+      <c r="E12" s="29"/>
+      <c r="F12" s="29"/>
+      <c r="G12" s="29"/>
     </row>
     <row r="13" spans="1:7">
-      <c r="A13" t="s">
-        <v>19</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="C13" t="str">
-        <f>_xlfn.CONCAT("b 0x",A46)</f>
-        <v>b 0x004B9FD0</v>
-      </c>
-      <c r="E13" t="s">
-        <v>79</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="G13" t="str">
-        <f>_xlfn.CONCAT("b 0x",E46)</f>
-        <v>b 0x004B9FD0</v>
+      <c r="A13" s="25" t="s">
+        <v>17</v>
+      </c>
+      <c r="B13" s="26" t="s">
+        <v>153</v>
+      </c>
+      <c r="C13" s="25" t="str">
+        <f>_xlfn.CONCAT("b 0x",A49)</f>
+        <v>b 0x004B9FDC</v>
+      </c>
+      <c r="E13" s="25" t="s">
+        <v>59</v>
+      </c>
+      <c r="F13" s="26" t="s">
+        <v>150</v>
+      </c>
+      <c r="G13" s="25" t="str">
+        <f>_xlfn.CONCAT("b 0x",E49)</f>
+        <v>b 0x004B9FDC</v>
       </c>
     </row>
     <row r="14" spans="1:7">
-      <c r="A14" t="str">
+      <c r="A14" s="25" t="str">
         <f t="shared" ref="A14" si="2">DEC2HEX(HEX2DEC(A13)+4,8)</f>
         <v>003417DC</v>
       </c>
-      <c r="B14" t="s">
-        <v>11</v>
-      </c>
-      <c r="C14" t="s">
+      <c r="B14" s="25" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="25" t="s">
         <v>4</v>
       </c>
-      <c r="E14" t="str">
+      <c r="E14" s="25" t="str">
         <f t="shared" ref="E14" si="3">DEC2HEX(HEX2DEC(E13)+4,8)</f>
         <v>003417E0</v>
       </c>
-      <c r="F14" t="s">
-        <v>11</v>
-      </c>
-      <c r="G14" t="s">
+      <c r="F14" s="25" t="s">
+        <v>9</v>
+      </c>
+      <c r="G14" s="25" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="16" spans="1:7">
-      <c r="A16" s="16" t="s">
-        <v>89</v>
-      </c>
-      <c r="B16" s="16"/>
-      <c r="C16" s="16"/>
-      <c r="D16" s="16"/>
-      <c r="E16" s="16"/>
-      <c r="F16" s="16"/>
-      <c r="G16" s="16"/>
+      <c r="A16" s="29" t="s">
+        <v>68</v>
+      </c>
+      <c r="B16" s="29"/>
+      <c r="C16" s="29"/>
+      <c r="D16" s="29"/>
+      <c r="E16" s="29"/>
+      <c r="F16" s="29"/>
+      <c r="G16" s="29"/>
     </row>
     <row r="17" spans="1:7">
-      <c r="A17" t="s">
-        <v>90</v>
-      </c>
-      <c r="B17" t="s">
-        <v>92</v>
-      </c>
-      <c r="C17" t="s">
-        <v>91</v>
-      </c>
-      <c r="E17" t="str">
+      <c r="A17" s="25" t="s">
+        <v>69</v>
+      </c>
+      <c r="B17" s="25" t="s">
+        <v>71</v>
+      </c>
+      <c r="C17" s="25" t="s">
+        <v>70</v>
+      </c>
+      <c r="E17" s="25" t="str">
         <f>DEC2HEX(HEX2DEC(A17)-HEX2DEC(A14)+HEX2DEC(E14),8)</f>
         <v>003418F0</v>
       </c>
-      <c r="F17" t="s">
-        <v>92</v>
-      </c>
-      <c r="G17" t="s">
-        <v>91</v>
+      <c r="F17" s="25" t="s">
+        <v>71</v>
+      </c>
+      <c r="G17" s="25" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="21" spans="1:7" hidden="1">
-      <c r="A21" s="16" t="s">
-        <v>25</v>
-      </c>
-      <c r="B21" s="16"/>
-      <c r="C21" s="16"/>
-      <c r="D21" s="16"/>
-      <c r="E21" s="16"/>
-      <c r="F21" s="16"/>
-      <c r="G21" s="16"/>
+      <c r="A21" s="29" t="s">
+        <v>23</v>
+      </c>
+      <c r="B21" s="29"/>
+      <c r="C21" s="29"/>
+      <c r="D21" s="29"/>
+      <c r="E21" s="29"/>
+      <c r="F21" s="29"/>
+      <c r="G21" s="29"/>
     </row>
     <row r="22" spans="1:7" hidden="1">
-      <c r="A22" t="s">
-        <v>30</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="C22" t="s">
+      <c r="A22" s="25" t="s">
+        <v>28</v>
+      </c>
+      <c r="B22" s="26" t="s">
         <v>38</v>
       </c>
-      <c r="E22" t="s">
-        <v>80</v>
-      </c>
-      <c r="F22" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="G22" t="s">
+      <c r="C22" s="25" t="s">
+        <v>35</v>
+      </c>
+      <c r="E22" s="25" t="s">
+        <v>60</v>
+      </c>
+      <c r="F22" s="26" t="s">
         <v>38</v>
       </c>
+      <c r="G22" s="25" t="s">
+        <v>35</v>
+      </c>
     </row>
     <row r="23" spans="1:7" hidden="1">
-      <c r="B23" s="3"/>
-      <c r="F23" s="3"/>
+      <c r="B23" s="27"/>
+      <c r="F23" s="27"/>
     </row>
     <row r="24" spans="1:7">
-      <c r="A24" s="16" t="s">
-        <v>28</v>
-      </c>
-      <c r="B24" s="16"/>
-      <c r="C24" s="16"/>
-      <c r="D24" s="16"/>
-      <c r="E24" s="16"/>
-      <c r="F24" s="16"/>
-      <c r="G24" s="16"/>
+      <c r="A24" s="29" t="s">
+        <v>26</v>
+      </c>
+      <c r="B24" s="29"/>
+      <c r="C24" s="29"/>
+      <c r="D24" s="29"/>
+      <c r="E24" s="29"/>
+      <c r="F24" s="29"/>
+      <c r="G24" s="29"/>
     </row>
     <row r="25" spans="1:7">
-      <c r="A25" t="s">
-        <v>72</v>
-      </c>
-      <c r="B25" t="s">
+      <c r="A25" s="25" t="s">
         <v>53</v>
       </c>
-      <c r="C25" t="s">
-        <v>31</v>
-      </c>
-      <c r="E25" t="s">
-        <v>72</v>
-      </c>
-      <c r="F25" t="s">
+      <c r="B25" s="25" t="s">
+        <v>33</v>
+      </c>
+      <c r="C25" s="25" t="s">
+        <v>32</v>
+      </c>
+      <c r="E25" s="25" t="s">
         <v>53</v>
       </c>
-      <c r="G25" t="s">
-        <v>31</v>
+      <c r="F25" s="25" t="str">
+        <f>B25</f>
+        <v>0CD04DE2</v>
+      </c>
+      <c r="G25" s="25" t="str">
+        <f>C25</f>
+        <v>sub sp, sp, #0xc</v>
       </c>
     </row>
     <row r="26" spans="1:7">
-      <c r="A26" t="str">
-        <f t="shared" ref="A26:A38" si="4">DEC2HEX(HEX2DEC(A25)+4,8)</f>
+      <c r="A26" s="25" t="str">
+        <f t="shared" ref="A26:A40" si="4">DEC2HEX(HEX2DEC(A25)+4,8)</f>
         <v>004B9F90</v>
       </c>
-      <c r="B26" t="s">
-        <v>57</v>
-      </c>
-      <c r="C26" t="str">
-        <f>_xlfn.CONCAT("ldr r2, [pc, 0x",DEC2HEX(HEX2DEC(A36)-HEX2DEC(A28)),"]")</f>
-        <v>ldr r2, [pc, 0x20]</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="E26" t="str">
-        <f t="shared" ref="E26:E38" si="5">DEC2HEX(HEX2DEC(E25)+4,8)</f>
+      <c r="B26" s="25" t="s">
+        <v>133</v>
+      </c>
+      <c r="C26" s="25" t="s">
+        <v>123</v>
+      </c>
+      <c r="D26" s="28"/>
+      <c r="E26" s="25" t="str">
+        <f t="shared" ref="E26:E41" si="5">DEC2HEX(HEX2DEC(E25)+4,8)</f>
         <v>004B9F90</v>
       </c>
-      <c r="F26" t="s">
-        <v>57</v>
-      </c>
-      <c r="G26" t="str">
-        <f>_xlfn.CONCAT("ldr r2, [pc, 0x",DEC2HEX(HEX2DEC(E36)-HEX2DEC(E28)),"]")</f>
-        <v>ldr r2, [pc, 0x20]</v>
+      <c r="F26" s="25" t="str">
+        <f t="shared" ref="F26:F40" si="6">B26</f>
+        <v>0C402DE9</v>
+      </c>
+      <c r="G26" s="25" t="str">
+        <f t="shared" ref="G26:G40" si="7">C26</f>
+        <v>push {r2, r3, lr}</v>
       </c>
     </row>
     <row r="27" spans="1:7">
-      <c r="A27" t="str">
+      <c r="A27" s="25" t="str">
         <f t="shared" si="4"/>
         <v>004B9F94</v>
       </c>
-      <c r="B27" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="C27" t="s">
-        <v>51</v>
-      </c>
-      <c r="D27" s="2"/>
-      <c r="E27" t="str">
+      <c r="B27" s="26" t="s">
+        <v>134</v>
+      </c>
+      <c r="C27" s="25" t="s">
+        <v>117</v>
+      </c>
+      <c r="D27" s="28" t="s">
+        <v>119</v>
+      </c>
+      <c r="E27" s="25" t="str">
         <f t="shared" si="5"/>
         <v>004B9F94</v>
       </c>
-      <c r="F27" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="G27" t="s">
-        <v>51</v>
+      <c r="F27" s="25" t="str">
+        <f t="shared" si="6"/>
+        <v>052B41E2</v>
+      </c>
+      <c r="G27" s="25" t="str">
+        <f t="shared" si="7"/>
+        <v>sub r2, r1, 0x1400</v>
       </c>
     </row>
     <row r="28" spans="1:7">
-      <c r="A28" t="str">
+      <c r="A28" s="25" t="str">
         <f t="shared" si="4"/>
         <v>004B9F98</v>
       </c>
-      <c r="B28" t="s">
-        <v>55</v>
-      </c>
-      <c r="C28" t="str">
-        <f>_xlfn.CONCAT("blt 0x",A$33)</f>
-        <v>blt 0x004B9FAC</v>
-      </c>
-      <c r="E28" t="str">
+      <c r="B28" s="25" t="s">
+        <v>135</v>
+      </c>
+      <c r="C28" s="25" t="s">
+        <v>118</v>
+      </c>
+      <c r="E28" s="25" t="str">
         <f t="shared" si="5"/>
         <v>004B9F98</v>
       </c>
-      <c r="F28" t="s">
-        <v>55</v>
-      </c>
-      <c r="G28" t="str">
-        <f>_xlfn.CONCAT("blt 0x",E$33)</f>
-        <v>blt 0x004B9FAC</v>
+      <c r="F28" s="25" t="str">
+        <f t="shared" si="6"/>
+        <v>AA2052E2</v>
+      </c>
+      <c r="G28" s="25" t="str">
+        <f t="shared" si="7"/>
+        <v>subs r2, r2, 0xAA</v>
       </c>
     </row>
     <row r="29" spans="1:7">
-      <c r="A29" t="str">
+      <c r="A29" s="25" t="str">
         <f t="shared" si="4"/>
         <v>004B9F9C</v>
       </c>
-      <c r="B29" t="s">
-        <v>58</v>
-      </c>
-      <c r="C29" t="str">
-        <f>_xlfn.CONCAT("ldr r2, [pc, 0x",DEC2HEX(HEX2DEC(A37)-HEX2DEC(A31)),"]")</f>
-        <v>ldr r2, [pc, 0x18]</v>
-      </c>
-      <c r="D29" t="s">
-        <v>52</v>
-      </c>
-      <c r="E29" t="str">
+      <c r="B29" s="25" t="s">
+        <v>136</v>
+      </c>
+      <c r="C29" s="25" t="str">
+        <f>_xlfn.CONCAT("blt 0x",A40)</f>
+        <v>blt 0x004B9FC8</v>
+      </c>
+      <c r="D29" s="25" t="s">
+        <v>120</v>
+      </c>
+      <c r="E29" s="25" t="str">
         <f t="shared" si="5"/>
         <v>004B9F9C</v>
       </c>
-      <c r="F29" t="s">
-        <v>58</v>
-      </c>
-      <c r="G29" t="str">
-        <f>_xlfn.CONCAT("ldr r2, [pc, 0x",DEC2HEX(HEX2DEC(E37)-HEX2DEC(E31)),"]")</f>
-        <v>ldr r2, [pc, 0x18]</v>
+      <c r="F29" s="25" t="str">
+        <f t="shared" si="6"/>
+        <v>090000BA</v>
+      </c>
+      <c r="G29" s="25" t="str">
+        <f t="shared" si="7"/>
+        <v>blt 0x004B9FC8</v>
       </c>
     </row>
     <row r="30" spans="1:7">
-      <c r="A30" t="str">
+      <c r="A30" s="25" t="str">
         <f t="shared" si="4"/>
         <v>004B9FA0</v>
       </c>
-      <c r="B30" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="C30" t="s">
-        <v>51</v>
-      </c>
-      <c r="E30" t="str">
+      <c r="B30" s="26" t="s">
+        <v>137</v>
+      </c>
+      <c r="C30" s="25" t="s">
+        <v>121</v>
+      </c>
+      <c r="E30" s="25" t="str">
         <f t="shared" si="5"/>
         <v>004B9FA0</v>
       </c>
-      <c r="F30" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="G30" t="s">
-        <v>51</v>
+      <c r="F30" s="25" t="str">
+        <f t="shared" si="6"/>
+        <v>0E0052E3</v>
+      </c>
+      <c r="G30" s="25" t="str">
+        <f t="shared" si="7"/>
+        <v>cmp r2, 0xE</v>
       </c>
     </row>
     <row r="31" spans="1:7">
-      <c r="A31" t="str">
+      <c r="A31" s="25" t="str">
         <f t="shared" si="4"/>
         <v>004B9FA4</v>
       </c>
-      <c r="B31" t="s">
-        <v>56</v>
-      </c>
-      <c r="C31" t="str">
-        <f>_xlfn.CONCAT("bgt 0x",A$33)</f>
-        <v>bgt 0x004B9FAC</v>
-      </c>
-      <c r="E31" t="str">
+      <c r="B31" s="26" t="s">
+        <v>138</v>
+      </c>
+      <c r="C31" s="25" t="str">
+        <f>_xlfn.CONCAT("bhi 0x",A40)</f>
+        <v>bhi 0x004B9FC8</v>
+      </c>
+      <c r="D31" s="25" t="s">
+        <v>128</v>
+      </c>
+      <c r="E31" s="25" t="str">
         <f t="shared" si="5"/>
         <v>004B9FA4</v>
       </c>
-      <c r="F31" t="s">
-        <v>56</v>
-      </c>
-      <c r="G31" t="str">
-        <f>_xlfn.CONCAT("bgt 0x",E$33)</f>
-        <v>bgt 0x004B9FAC</v>
+      <c r="F31" s="25" t="str">
+        <f t="shared" si="6"/>
+        <v>0700008A</v>
+      </c>
+      <c r="G31" s="25" t="str">
+        <f t="shared" si="7"/>
+        <v>bhi 0x004B9FC8</v>
       </c>
     </row>
     <row r="32" spans="1:7">
-      <c r="A32" t="str">
+      <c r="A32" s="25" t="str">
         <f t="shared" si="4"/>
         <v>004B9FA8</v>
       </c>
-      <c r="B32" t="s">
-        <v>59</v>
-      </c>
-      <c r="C32" t="str">
-        <f>_xlfn.CONCAT("ldr r1, [pc, 0x",DEC2HEX(HEX2DEC(A38)-HEX2DEC(A34)),"]")</f>
-        <v>ldr r1, [pc, 0x10]</v>
-      </c>
-      <c r="E32" t="str">
+      <c r="B32" s="26" t="s">
+        <v>139</v>
+      </c>
+      <c r="C32" s="25" t="s">
+        <v>124</v>
+      </c>
+      <c r="E32" s="25" t="str">
         <f t="shared" si="5"/>
         <v>004B9FA8</v>
       </c>
-      <c r="F32" t="s">
-        <v>59</v>
-      </c>
-      <c r="G32" t="str">
-        <f>_xlfn.CONCAT("ldr r1, [pc, 0x",DEC2HEX(HEX2DEC(E38)-HEX2DEC(E34)),"]")</f>
-        <v>ldr r1, [pc, 0x10]</v>
+      <c r="F32" s="25" t="str">
+        <f t="shared" si="6"/>
+        <v>033002E2</v>
+      </c>
+      <c r="G32" s="25" t="str">
+        <f t="shared" si="7"/>
+        <v>and r3, r2, 0x3</v>
       </c>
     </row>
     <row r="33" spans="1:7">
-      <c r="A33" t="str">
+      <c r="A33" s="25" t="str">
         <f t="shared" si="4"/>
         <v>004B9FAC</v>
       </c>
-      <c r="B33" t="s">
-        <v>10</v>
-      </c>
-      <c r="C33" t="s">
-        <v>7</v>
-      </c>
-      <c r="E33" t="str">
+      <c r="B33" s="26" t="s">
+        <v>140</v>
+      </c>
+      <c r="C33" s="25" t="s">
+        <v>122</v>
+      </c>
+      <c r="E33" s="25" t="str">
         <f t="shared" si="5"/>
         <v>004B9FAC</v>
       </c>
-      <c r="F33" t="s">
-        <v>10</v>
-      </c>
-      <c r="G33" t="s">
-        <v>7</v>
+      <c r="F33" s="25" t="str">
+        <f t="shared" si="6"/>
+        <v>2221A0E1</v>
+      </c>
+      <c r="G33" s="25" t="str">
+        <f t="shared" si="7"/>
+        <v>lsr r2, r2, #2</v>
       </c>
     </row>
     <row r="34" spans="1:7">
-      <c r="A34" t="str">
+      <c r="A34" s="25" t="str">
         <f t="shared" si="4"/>
         <v>004B9FB0</v>
       </c>
-      <c r="B34" t="s">
-        <v>36</v>
-      </c>
-      <c r="C34" t="s">
-        <v>35</v>
-      </c>
-      <c r="E34" t="str">
+      <c r="B34" s="26" t="s">
+        <v>141</v>
+      </c>
+      <c r="C34" s="25" t="s">
+        <v>125</v>
+      </c>
+      <c r="E34" s="25" t="str">
         <f t="shared" si="5"/>
         <v>004B9FB0</v>
       </c>
-      <c r="F34" t="s">
-        <v>36</v>
-      </c>
-      <c r="G34" t="s">
-        <v>35</v>
+      <c r="F34" s="25" t="str">
+        <f t="shared" si="6"/>
+        <v>033082E0</v>
+      </c>
+      <c r="G34" s="25" t="str">
+        <f t="shared" si="7"/>
+        <v>add r3, r2, r3</v>
       </c>
     </row>
     <row r="35" spans="1:7">
-      <c r="A35" t="str">
+      <c r="A35" s="25" t="str">
         <f t="shared" si="4"/>
         <v>004B9FB4</v>
       </c>
-      <c r="B35" t="s">
-        <v>12</v>
-      </c>
-      <c r="C35" t="s">
-        <v>5</v>
-      </c>
-      <c r="E35" t="str">
+      <c r="B35" s="26" t="s">
+        <v>142</v>
+      </c>
+      <c r="C35" s="25" t="s">
+        <v>126</v>
+      </c>
+      <c r="E35" s="25" t="str">
         <f t="shared" si="5"/>
         <v>004B9FB4</v>
       </c>
-      <c r="F35" t="s">
-        <v>12</v>
-      </c>
-      <c r="G35" t="s">
-        <v>5</v>
+      <c r="F35" s="25" t="str">
+        <f t="shared" si="6"/>
+        <v>030053E3</v>
+      </c>
+      <c r="G35" s="25" t="str">
+        <f t="shared" si="7"/>
+        <v>cmp r3, 0x3</v>
       </c>
     </row>
     <row r="36" spans="1:7">
-      <c r="A36" t="str">
+      <c r="A36" s="25" t="str">
         <f t="shared" si="4"/>
         <v>004B9FB8</v>
       </c>
-      <c r="B36" t="s">
-        <v>48</v>
-      </c>
-      <c r="D36" t="s">
-        <v>44</v>
-      </c>
-      <c r="E36" t="str">
+      <c r="B36" s="26" t="s">
+        <v>143</v>
+      </c>
+      <c r="C36" s="25" t="s">
+        <v>127</v>
+      </c>
+      <c r="E36" s="25" t="str">
         <f t="shared" si="5"/>
         <v>004B9FB8</v>
       </c>
-      <c r="F36" t="s">
-        <v>48</v>
+      <c r="F36" s="25" t="str">
+        <f t="shared" si="6"/>
+        <v>03304322</v>
+      </c>
+      <c r="G36" s="25" t="str">
+        <f t="shared" si="7"/>
+        <v>subhs r3, r3, 0x3</v>
       </c>
     </row>
     <row r="37" spans="1:7">
-      <c r="A37" t="str">
+      <c r="A37" s="25" t="str">
         <f t="shared" si="4"/>
         <v>004B9FBC</v>
       </c>
-      <c r="B37" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="D37" t="s">
-        <v>45</v>
-      </c>
-      <c r="E37" t="str">
+      <c r="B37" s="26" t="s">
+        <v>144</v>
+      </c>
+      <c r="C37" s="25" t="s">
+        <v>129</v>
+      </c>
+      <c r="D37" s="25" t="s">
+        <v>113</v>
+      </c>
+      <c r="E37" s="25" t="str">
         <f t="shared" si="5"/>
         <v>004B9FBC</v>
       </c>
-      <c r="F37" s="1" t="s">
-        <v>47</v>
+      <c r="F37" s="25" t="str">
+        <f t="shared" si="6"/>
+        <v>010053E3</v>
+      </c>
+      <c r="G37" s="25" t="str">
+        <f t="shared" si="7"/>
+        <v>cmp r3, 0x1</v>
       </c>
     </row>
     <row r="38" spans="1:7">
-      <c r="A38" t="str">
+      <c r="A38" s="25" t="str">
         <f t="shared" si="4"/>
         <v>004B9FC0</v>
       </c>
-      <c r="B38" t="s">
-        <v>49</v>
-      </c>
-      <c r="D38" t="s">
-        <v>46</v>
-      </c>
-      <c r="E38" t="str">
+      <c r="B38" s="26" t="s">
+        <v>145</v>
+      </c>
+      <c r="C38" s="25" t="str">
+        <f>_xlfn.CONCAT("ldrhlo r1, [pc, #",HEX2DEC(A$41)-HEX2DEC(A38)-8,"]")</f>
+        <v>ldrhlo r1, [pc, #4]</v>
+      </c>
+      <c r="D38" s="25" t="s">
+        <v>132</v>
+      </c>
+      <c r="E38" s="25" t="str">
         <f t="shared" si="5"/>
         <v>004B9FC0</v>
       </c>
-      <c r="F38" t="s">
-        <v>49</v>
+      <c r="F38" s="25" t="str">
+        <f t="shared" si="6"/>
+        <v>B410DF31</v>
+      </c>
+      <c r="G38" s="25" t="str">
+        <f t="shared" si="7"/>
+        <v>ldrhlo r1, [pc, #4]</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7">
+      <c r="A39" s="25" t="str">
+        <f t="shared" si="4"/>
+        <v>004B9FC4</v>
+      </c>
+      <c r="B39" s="26" t="s">
+        <v>146</v>
+      </c>
+      <c r="C39" s="25" t="str">
+        <f>_xlfn.CONCAT("ldrhhi r1, [pc, #",HEX2DEC(A$41)-HEX2DEC(A39)-8+2,"]")</f>
+        <v>ldrhhi r1, [pc, #2]</v>
+      </c>
+      <c r="E39" s="25" t="str">
+        <f t="shared" si="5"/>
+        <v>004B9FC4</v>
+      </c>
+      <c r="F39" s="25" t="str">
+        <f t="shared" si="6"/>
+        <v>B210DF81</v>
+      </c>
+      <c r="G39" s="25" t="str">
+        <f t="shared" si="7"/>
+        <v>ldrhhi r1, [pc, #2]</v>
       </c>
     </row>
     <row r="40" spans="1:7">
-      <c r="A40" s="16" t="s">
-        <v>60</v>
-      </c>
-      <c r="B40" s="16"/>
-      <c r="C40" s="16"/>
-      <c r="D40" s="16"/>
-      <c r="E40" s="16"/>
-      <c r="F40" s="16"/>
-      <c r="G40" s="16"/>
+      <c r="A40" s="25" t="str">
+        <f t="shared" si="4"/>
+        <v>004B9FC8</v>
+      </c>
+      <c r="B40" s="26" t="s">
+        <v>147</v>
+      </c>
+      <c r="C40" s="25" t="str">
+        <f>SUBSTITUTE(SUBSTITUTE(C26,"push","pop"),"lr","pc")</f>
+        <v>pop {r2, r3, pc}</v>
+      </c>
+      <c r="E40" s="25" t="str">
+        <f t="shared" si="5"/>
+        <v>004B9FC8</v>
+      </c>
+      <c r="F40" s="25" t="str">
+        <f t="shared" si="6"/>
+        <v>0C80BDE8</v>
+      </c>
+      <c r="G40" s="25" t="str">
+        <f t="shared" si="7"/>
+        <v>pop {r2, r3, pc}</v>
+      </c>
     </row>
     <row r="41" spans="1:7">
-      <c r="A41" t="str">
-        <f>DEC2HEX(HEX2DEC(A38)+4,8)</f>
-        <v>004B9FC4</v>
-      </c>
-      <c r="B41" t="s">
-        <v>96</v>
-      </c>
-      <c r="C41" t="s">
-        <v>85</v>
-      </c>
-      <c r="D41" t="s">
-        <v>93</v>
-      </c>
-      <c r="E41" t="str">
-        <f>DEC2HEX(HEX2DEC(E38)+4,8)</f>
-        <v>004B9FC4</v>
-      </c>
-      <c r="F41" t="s">
-        <v>96</v>
-      </c>
-      <c r="G41" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7">
-      <c r="A42" t="str">
-        <f t="shared" ref="A42:A43" si="6">DEC2HEX(HEX2DEC(A41)+4,8)</f>
-        <v>004B9FC8</v>
-      </c>
-      <c r="B42" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="C42" t="s">
-        <v>35</v>
-      </c>
-      <c r="D42" t="s">
-        <v>94</v>
-      </c>
-      <c r="E42" t="str">
-        <f t="shared" ref="E42:E43" si="7">DEC2HEX(HEX2DEC(E41)+4,8)</f>
-        <v>004B9FC8</v>
-      </c>
-      <c r="F42" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="G42" t="s">
-        <v>35</v>
+      <c r="A41" s="25" t="str">
+        <f>DEC2HEX(HEX2DEC(A40)+4,8)</f>
+        <v>004B9FCC</v>
+      </c>
+      <c r="B41" s="25" t="s">
+        <v>130</v>
+      </c>
+      <c r="D41" s="25" t="s">
+        <v>131</v>
+      </c>
+      <c r="E41" s="25" t="str">
+        <f t="shared" si="5"/>
+        <v>004B9FCC</v>
+      </c>
+      <c r="F41" s="25" t="str">
+        <f>B41</f>
+        <v>7C151716</v>
       </c>
     </row>
     <row r="43" spans="1:7">
-      <c r="A43" t="str">
-        <f t="shared" si="6"/>
-        <v>004B9FCC</v>
-      </c>
-      <c r="B43" t="s">
-        <v>12</v>
-      </c>
-      <c r="C43" t="s">
-        <v>5</v>
-      </c>
-      <c r="D43" t="s">
-        <v>95</v>
-      </c>
-      <c r="E43" t="str">
-        <f t="shared" si="7"/>
-        <v>004B9FCC</v>
-      </c>
-      <c r="F43" t="s">
-        <v>12</v>
-      </c>
-      <c r="G43" t="s">
-        <v>5</v>
+      <c r="A43" s="24" t="s">
+        <v>41</v>
+      </c>
+      <c r="B43" s="24"/>
+      <c r="E43" s="24"/>
+      <c r="F43" s="24"/>
+      <c r="G43" s="24"/>
+    </row>
+    <row r="44" spans="1:7">
+      <c r="A44" s="25" t="str">
+        <f>DEC2HEX(HEX2DEC(A41)+4,8)</f>
+        <v>004B9FD0</v>
+      </c>
+      <c r="B44" s="25" t="s">
+        <v>75</v>
+      </c>
+      <c r="C44" s="25" t="s">
+        <v>64</v>
+      </c>
+      <c r="D44" s="25" t="s">
+        <v>72</v>
+      </c>
+      <c r="E44" s="25" t="str">
+        <f>DEC2HEX(HEX2DEC(E41)+4,8)</f>
+        <v>004B9FD0</v>
+      </c>
+      <c r="F44" s="25" t="s">
+        <v>75</v>
+      </c>
+      <c r="G44" s="25" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="45" spans="1:7">
-      <c r="A45" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="B45" s="16"/>
-      <c r="C45" s="16"/>
-      <c r="D45" s="16"/>
-      <c r="E45" s="16"/>
-      <c r="F45" s="16"/>
-      <c r="G45" s="16"/>
+      <c r="A45" s="25" t="str">
+        <f t="shared" ref="A45:A46" si="8">DEC2HEX(HEX2DEC(A44)+4,8)</f>
+        <v>004B9FD4</v>
+      </c>
+      <c r="B45" s="26" t="s">
+        <v>33</v>
+      </c>
+      <c r="C45" s="25" t="s">
+        <v>32</v>
+      </c>
+      <c r="D45" s="25" t="s">
+        <v>73</v>
+      </c>
+      <c r="E45" s="25" t="str">
+        <f t="shared" ref="E45:E46" si="9">DEC2HEX(HEX2DEC(E44)+4,8)</f>
+        <v>004B9FD4</v>
+      </c>
+      <c r="F45" s="26" t="s">
+        <v>33</v>
+      </c>
+      <c r="G45" s="25" t="s">
+        <v>32</v>
+      </c>
     </row>
     <row r="46" spans="1:7">
-      <c r="A46" t="str">
-        <f>DEC2HEX(HEX2DEC(A43)+4,8)</f>
-        <v>004B9FD0</v>
-      </c>
-      <c r="B46" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="C46" t="s">
-        <v>62</v>
-      </c>
-      <c r="D46" s="2"/>
-      <c r="E46" t="str">
-        <f>DEC2HEX(HEX2DEC(E43)+4,8)</f>
-        <v>004B9FD0</v>
-      </c>
-      <c r="F46" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="G46" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7">
-      <c r="A47" t="str">
-        <f t="shared" ref="A47:A54" si="8">DEC2HEX(HEX2DEC(A46)+4,8)</f>
-        <v>004B9FD4</v>
-      </c>
-      <c r="B47" t="s">
-        <v>68</v>
-      </c>
-      <c r="C47" t="s">
-        <v>63</v>
-      </c>
-      <c r="E47" t="str">
-        <f t="shared" ref="E47:E54" si="9">DEC2HEX(HEX2DEC(E46)+4,8)</f>
-        <v>004B9FD4</v>
-      </c>
-      <c r="F47" t="s">
-        <v>68</v>
-      </c>
-      <c r="G47" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7">
-      <c r="A48" t="str">
+      <c r="A46" s="25" t="str">
         <f t="shared" si="8"/>
         <v>004B9FD8</v>
       </c>
-      <c r="B48" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="C48" t="s">
-        <v>86</v>
-      </c>
-      <c r="E48" t="str">
+      <c r="B46" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="C46" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="D46" s="25" t="s">
+        <v>74</v>
+      </c>
+      <c r="E46" s="25" t="str">
         <f t="shared" si="9"/>
         <v>004B9FD8</v>
       </c>
-      <c r="F48" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="G48" t="s">
-        <v>86</v>
-      </c>
+      <c r="F46" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="G46" s="25" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7">
+      <c r="A48" s="24" t="s">
+        <v>42</v>
+      </c>
+      <c r="B48" s="24"/>
+      <c r="E48" s="24"/>
+      <c r="F48" s="24"/>
+      <c r="G48" s="24"/>
     </row>
     <row r="49" spans="1:7">
-      <c r="A49" t="str">
-        <f t="shared" si="8"/>
+      <c r="A49" s="25" t="str">
+        <f>DEC2HEX(HEX2DEC(A46)+4,8)</f>
         <v>004B9FDC</v>
       </c>
-      <c r="B49" t="s">
-        <v>97</v>
-      </c>
-      <c r="C49" t="str">
+      <c r="B49" s="26" t="s">
+        <v>48</v>
+      </c>
+      <c r="C49" s="25" t="s">
+        <v>43</v>
+      </c>
+      <c r="D49" s="28"/>
+      <c r="E49" s="25" t="str">
+        <f>DEC2HEX(HEX2DEC(E46)+4,8)</f>
+        <v>004B9FDC</v>
+      </c>
+      <c r="F49" s="26" t="s">
+        <v>48</v>
+      </c>
+      <c r="G49" s="25" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7">
+      <c r="A50" s="25" t="str">
+        <f t="shared" ref="A50:A57" si="10">DEC2HEX(HEX2DEC(A49)+4,8)</f>
+        <v>004B9FE0</v>
+      </c>
+      <c r="B50" s="25" t="s">
+        <v>49</v>
+      </c>
+      <c r="C50" s="25" t="s">
+        <v>44</v>
+      </c>
+      <c r="E50" s="25" t="str">
+        <f t="shared" ref="E50:E57" si="11">DEC2HEX(HEX2DEC(E49)+4,8)</f>
+        <v>004B9FE0</v>
+      </c>
+      <c r="F50" s="25" t="s">
+        <v>49</v>
+      </c>
+      <c r="G50" s="25" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7">
+      <c r="A51" s="25" t="str">
+        <f t="shared" si="10"/>
+        <v>004B9FE4</v>
+      </c>
+      <c r="B51" s="26" t="s">
+        <v>66</v>
+      </c>
+      <c r="C51" s="25" t="s">
+        <v>65</v>
+      </c>
+      <c r="E51" s="25" t="str">
+        <f t="shared" si="11"/>
+        <v>004B9FE4</v>
+      </c>
+      <c r="F51" s="26" t="s">
+        <v>66</v>
+      </c>
+      <c r="G51" s="25" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7">
+      <c r="A52" s="25" t="str">
+        <f t="shared" si="10"/>
+        <v>004B9FE8</v>
+      </c>
+      <c r="B52" s="25" t="s">
+        <v>152</v>
+      </c>
+      <c r="C52" s="25" t="str">
         <f>_xlfn.CONCAT("bl 0x",A6)</f>
         <v>bl 0x002238C0</v>
       </c>
-      <c r="E49" t="str">
-        <f t="shared" si="9"/>
-        <v>004B9FDC</v>
-      </c>
-      <c r="F49" t="s">
-        <v>97</v>
-      </c>
-      <c r="G49" t="str">
+      <c r="E52" s="25" t="str">
+        <f t="shared" si="11"/>
+        <v>004B9FE8</v>
+      </c>
+      <c r="F52" s="25" t="s">
+        <v>152</v>
+      </c>
+      <c r="G52" s="25" t="str">
         <f>_xlfn.CONCAT("bl 0x",E6)</f>
         <v>bl 0x002238C0</v>
       </c>
     </row>
-    <row r="50" spans="1:7">
-      <c r="A50" t="str">
-        <f t="shared" si="8"/>
-        <v>004B9FE0</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="C50" t="s">
+    <row r="53" spans="1:7">
+      <c r="A53" s="25" t="str">
+        <f t="shared" si="10"/>
+        <v>004B9FEC</v>
+      </c>
+      <c r="B53" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="D50" t="s">
-        <v>64</v>
-      </c>
-      <c r="E50" t="str">
-        <f t="shared" si="9"/>
-        <v>004B9FE0</v>
-      </c>
-      <c r="F50" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="G50" t="s">
+      <c r="C53" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="D53" s="25" t="s">
+        <v>45</v>
+      </c>
+      <c r="E53" s="25" t="str">
+        <f t="shared" si="11"/>
+        <v>004B9FEC</v>
+      </c>
+      <c r="F53" s="26" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="51" spans="1:7">
-      <c r="A51" t="str">
-        <f t="shared" si="8"/>
-        <v>004B9FE4</v>
-      </c>
-      <c r="B51" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="C51" t="s">
-        <v>65</v>
-      </c>
-      <c r="E51" t="str">
-        <f t="shared" si="9"/>
-        <v>004B9FE4</v>
-      </c>
-      <c r="F51" t="s">
-        <v>69</v>
-      </c>
-      <c r="G51" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7">
-      <c r="A52" t="str">
-        <f t="shared" si="8"/>
-        <v>004B9FE8</v>
-      </c>
-      <c r="B52" t="s">
-        <v>98</v>
-      </c>
-      <c r="C52" t="str">
+      <c r="G53" s="25" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7">
+      <c r="A54" s="25" t="str">
+        <f t="shared" si="10"/>
+        <v>004B9FF0</v>
+      </c>
+      <c r="B54" s="26" t="s">
+        <v>50</v>
+      </c>
+      <c r="C54" s="25" t="s">
+        <v>46</v>
+      </c>
+      <c r="E54" s="25" t="str">
+        <f t="shared" si="11"/>
+        <v>004B9FF0</v>
+      </c>
+      <c r="F54" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="G54" s="25" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7">
+      <c r="A55" s="25" t="str">
+        <f t="shared" si="10"/>
+        <v>004B9FF4</v>
+      </c>
+      <c r="B55" s="25" t="s">
+        <v>155</v>
+      </c>
+      <c r="C55" s="25" t="str">
         <f>_xlfn.CONCAT("blt 0x",A22)</f>
         <v>blt 0x003418C4</v>
       </c>
-      <c r="E52" t="str">
-        <f t="shared" si="9"/>
-        <v>004B9FE8</v>
-      </c>
-      <c r="F52" t="s">
-        <v>100</v>
-      </c>
-      <c r="G52" t="str">
+      <c r="E55" s="25" t="str">
+        <f t="shared" si="11"/>
+        <v>004B9FF4</v>
+      </c>
+      <c r="F55" s="25" t="s">
+        <v>148</v>
+      </c>
+      <c r="G55" s="25" t="str">
         <f>_xlfn.CONCAT("blt 0x",E22)</f>
         <v>blt 0x003418C8</v>
       </c>
     </row>
-    <row r="53" spans="1:7">
-      <c r="A53" t="str">
-        <f t="shared" si="8"/>
-        <v>004B9FEC</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C53" t="s">
-        <v>66</v>
-      </c>
-      <c r="D53" t="s">
-        <v>70</v>
-      </c>
-      <c r="E53" t="str">
-        <f t="shared" si="9"/>
-        <v>004B9FEC</v>
-      </c>
-      <c r="F53" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="G53" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7">
-      <c r="A54" t="str">
-        <f t="shared" si="8"/>
-        <v>004B9FF0</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="C54" t="str">
+    <row r="56" spans="1:7">
+      <c r="A56" s="25" t="str">
+        <f t="shared" si="10"/>
+        <v>004B9FF8</v>
+      </c>
+      <c r="B56" s="26" t="s">
+        <v>12</v>
+      </c>
+      <c r="C56" s="25" t="s">
+        <v>47</v>
+      </c>
+      <c r="D56" s="25" t="s">
+        <v>51</v>
+      </c>
+      <c r="E56" s="25" t="str">
+        <f t="shared" si="11"/>
+        <v>004B9FF8</v>
+      </c>
+      <c r="F56" s="26" t="s">
+        <v>12</v>
+      </c>
+      <c r="G56" s="25" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7">
+      <c r="A57" s="25" t="str">
+        <f t="shared" si="10"/>
+        <v>004B9FFC</v>
+      </c>
+      <c r="B57" s="26" t="s">
+        <v>156</v>
+      </c>
+      <c r="C57" s="25" t="str">
         <f>_xlfn.CONCAT("b 0x",A14)</f>
         <v>b 0x003417DC</v>
       </c>
-      <c r="D54" t="s">
-        <v>71</v>
-      </c>
-      <c r="E54" t="str">
-        <f t="shared" si="9"/>
-        <v>004B9FF0</v>
-      </c>
-      <c r="F54" t="s">
-        <v>101</v>
-      </c>
-      <c r="G54" t="str">
+      <c r="D57" s="25" t="s">
+        <v>52</v>
+      </c>
+      <c r="E57" s="25" t="str">
+        <f t="shared" si="11"/>
+        <v>004B9FFC</v>
+      </c>
+      <c r="F57" s="25" t="s">
+        <v>149</v>
+      </c>
+      <c r="G57" s="25" t="str">
         <f>_xlfn.CONCAT("b 0x",E14)</f>
         <v>b 0x003417E0</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="9">
-    <mergeCell ref="A45:G45"/>
-    <mergeCell ref="A40:G40"/>
+  <mergeCells count="7">
+    <mergeCell ref="A24:G24"/>
+    <mergeCell ref="A16:G16"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A5:G5"/>
     <mergeCell ref="A8:G8"/>
     <mergeCell ref="A12:G12"/>
     <mergeCell ref="A21:G21"/>
-    <mergeCell ref="A24:G24"/>
-    <mergeCell ref="A16:G16"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -2081,60 +2368,800 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6D1D277-C753-4CC2-B4A8-935BAA61127D}">
+  <dimension ref="A1:M21"/>
+  <sheetFormatPr defaultRowHeight="14.15"/>
+  <cols>
+    <col min="1" max="1" width="4.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.35546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:13" ht="14.6" thickTop="1">
+      <c r="A1" s="14" t="s">
+        <v>112</v>
+      </c>
+      <c r="B1" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="16" t="s">
+        <v>96</v>
+      </c>
+      <c r="E1" s="23" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
+      <c r="A2" s="17" t="s">
+        <v>81</v>
+      </c>
+      <c r="B2" s="18" t="str">
+        <f>DEC2HEX(A2)</f>
+        <v>14AA</v>
+      </c>
+      <c r="C2" s="19" t="s">
+        <v>97</v>
+      </c>
+      <c r="E2">
+        <f>M2</f>
+        <v>0</v>
+      </c>
+      <c r="F2" t="str">
+        <f>_xlfn.XLOOKUP(E2,D$19:D$21,C$19:C$21)</f>
+        <v>Move Relearner</v>
+      </c>
+      <c r="H2">
+        <f>A2-5290</f>
+        <v>0</v>
+      </c>
+      <c r="I2" t="str">
+        <f>DEC2HEX(H2)</f>
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <f>_xlfn.BITAND(H2,3)</f>
+        <v>0</v>
+      </c>
+      <c r="K2">
+        <f>_xlfn.BITRSHIFT(H2,2)</f>
+        <v>0</v>
+      </c>
+      <c r="L2">
+        <f>SUM(J2:K2)</f>
+        <v>0</v>
+      </c>
+      <c r="M2">
+        <f>IF(L2&gt;=3,L2-3,L2)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
+      <c r="A3" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="B3" s="18" t="str">
+        <f t="shared" ref="B3:B16" si="0">DEC2HEX(A3)</f>
+        <v>14AB</v>
+      </c>
+      <c r="C3" s="19" t="s">
+        <v>98</v>
+      </c>
+      <c r="E3">
+        <f t="shared" ref="E3:E16" si="1">M3</f>
+        <v>1</v>
+      </c>
+      <c r="F3" t="str">
+        <f t="shared" ref="F3:F16" si="2">_xlfn.XLOOKUP(E3,D$19:D$21,C$19:C$21)</f>
+        <v>Café</v>
+      </c>
+      <c r="H3">
+        <f t="shared" ref="H3:H16" si="3">A3-5290</f>
+        <v>1</v>
+      </c>
+      <c r="I3" t="str">
+        <f t="shared" ref="I3:I16" si="4">DEC2HEX(H3)</f>
+        <v>1</v>
+      </c>
+      <c r="J3">
+        <f t="shared" ref="J3:J16" si="5">_xlfn.BITAND(H3,3)</f>
+        <v>1</v>
+      </c>
+      <c r="K3">
+        <f t="shared" ref="K3:K16" si="6">_xlfn.BITRSHIFT(H3,2)</f>
+        <v>0</v>
+      </c>
+      <c r="L3">
+        <f t="shared" ref="L3:L16" si="7">SUM(J3:K3)</f>
+        <v>1</v>
+      </c>
+      <c r="M3">
+        <f t="shared" ref="M3:M16" si="8">IF(L3&gt;=3,L3-3,L3)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
+      <c r="A4" s="17" t="s">
+        <v>83</v>
+      </c>
+      <c r="B4" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v>14AC</v>
+      </c>
+      <c r="C4" s="19" t="s">
+        <v>99</v>
+      </c>
+      <c r="E4">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="F4" t="str">
+        <f t="shared" si="2"/>
+        <v>Super Training</v>
+      </c>
+      <c r="H4">
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
+      <c r="I4" t="str">
+        <f t="shared" si="4"/>
+        <v>2</v>
+      </c>
+      <c r="J4">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="K4">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="L4">
+        <f t="shared" si="7"/>
+        <v>2</v>
+      </c>
+      <c r="M4">
+        <f t="shared" si="8"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
+      <c r="A5" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="B5" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v>14AD</v>
+      </c>
+      <c r="C5" s="19" t="s">
+        <v>100</v>
+      </c>
+      <c r="E5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F5" t="str">
+        <f t="shared" si="2"/>
+        <v>Move Relearner</v>
+      </c>
+      <c r="H5">
+        <f t="shared" si="3"/>
+        <v>3</v>
+      </c>
+      <c r="I5" t="str">
+        <f t="shared" si="4"/>
+        <v>3</v>
+      </c>
+      <c r="J5">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="K5">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="L5">
+        <f t="shared" si="7"/>
+        <v>3</v>
+      </c>
+      <c r="M5">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
+      <c r="A6" s="17" t="s">
+        <v>85</v>
+      </c>
+      <c r="B6" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v>14AE</v>
+      </c>
+      <c r="C6" s="19" t="s">
+        <v>101</v>
+      </c>
+      <c r="E6">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="F6" t="str">
+        <f t="shared" si="2"/>
+        <v>Café</v>
+      </c>
+      <c r="H6">
+        <f t="shared" si="3"/>
+        <v>4</v>
+      </c>
+      <c r="I6" t="str">
+        <f t="shared" si="4"/>
+        <v>4</v>
+      </c>
+      <c r="J6">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="K6">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="L6">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="M6">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
+      <c r="A7" s="17" t="s">
+        <v>86</v>
+      </c>
+      <c r="B7" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v>14AF</v>
+      </c>
+      <c r="C7" s="19" t="s">
+        <v>102</v>
+      </c>
+      <c r="E7">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="F7" t="str">
+        <f t="shared" si="2"/>
+        <v>Super Training</v>
+      </c>
+      <c r="H7">
+        <f t="shared" si="3"/>
+        <v>5</v>
+      </c>
+      <c r="I7" t="str">
+        <f t="shared" si="4"/>
+        <v>5</v>
+      </c>
+      <c r="J7">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="K7">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="L7">
+        <f t="shared" si="7"/>
+        <v>2</v>
+      </c>
+      <c r="M7">
+        <f t="shared" si="8"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="B8" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v>14B0</v>
+      </c>
+      <c r="C8" s="19" t="s">
+        <v>103</v>
+      </c>
+      <c r="E8">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F8" t="str">
+        <f t="shared" si="2"/>
+        <v>Move Relearner</v>
+      </c>
+      <c r="H8">
+        <f t="shared" si="3"/>
+        <v>6</v>
+      </c>
+      <c r="I8" t="str">
+        <f t="shared" si="4"/>
+        <v>6</v>
+      </c>
+      <c r="J8">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="K8">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="L8">
+        <f t="shared" si="7"/>
+        <v>3</v>
+      </c>
+      <c r="M8">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
+      <c r="A9" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="B9" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v>14B1</v>
+      </c>
+      <c r="C9" s="19" t="s">
+        <v>104</v>
+      </c>
+      <c r="E9">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="F9" t="str">
+        <f t="shared" si="2"/>
+        <v>Café</v>
+      </c>
+      <c r="H9">
+        <f t="shared" si="3"/>
+        <v>7</v>
+      </c>
+      <c r="I9" t="str">
+        <f t="shared" si="4"/>
+        <v>7</v>
+      </c>
+      <c r="J9">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="K9">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="L9">
+        <f t="shared" si="7"/>
+        <v>4</v>
+      </c>
+      <c r="M9">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
+      <c r="A10" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="B10" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v>14B2</v>
+      </c>
+      <c r="C10" s="19" t="s">
+        <v>105</v>
+      </c>
+      <c r="E10">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="F10" t="str">
+        <f t="shared" si="2"/>
+        <v>Super Training</v>
+      </c>
+      <c r="H10">
+        <f t="shared" si="3"/>
+        <v>8</v>
+      </c>
+      <c r="I10" t="str">
+        <f t="shared" si="4"/>
+        <v>8</v>
+      </c>
+      <c r="J10">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="K10">
+        <f t="shared" si="6"/>
+        <v>2</v>
+      </c>
+      <c r="L10">
+        <f t="shared" si="7"/>
+        <v>2</v>
+      </c>
+      <c r="M10">
+        <f t="shared" si="8"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13">
+      <c r="A11" s="17" t="s">
+        <v>90</v>
+      </c>
+      <c r="B11" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v>14B3</v>
+      </c>
+      <c r="C11" s="19" t="s">
+        <v>111</v>
+      </c>
+      <c r="E11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F11" t="str">
+        <f t="shared" si="2"/>
+        <v>Move Relearner</v>
+      </c>
+      <c r="H11">
+        <f t="shared" si="3"/>
+        <v>9</v>
+      </c>
+      <c r="I11" t="str">
+        <f t="shared" si="4"/>
+        <v>9</v>
+      </c>
+      <c r="J11">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="K11">
+        <f t="shared" si="6"/>
+        <v>2</v>
+      </c>
+      <c r="L11">
+        <f t="shared" si="7"/>
+        <v>3</v>
+      </c>
+      <c r="M11">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13">
+      <c r="A12" s="17" t="s">
+        <v>91</v>
+      </c>
+      <c r="B12" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v>14B4</v>
+      </c>
+      <c r="C12" s="19" t="s">
+        <v>106</v>
+      </c>
+      <c r="E12">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="F12" t="str">
+        <f t="shared" si="2"/>
+        <v>Café</v>
+      </c>
+      <c r="H12">
+        <f t="shared" si="3"/>
+        <v>10</v>
+      </c>
+      <c r="I12" t="str">
+        <f t="shared" si="4"/>
+        <v>A</v>
+      </c>
+      <c r="J12">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="K12">
+        <f t="shared" si="6"/>
+        <v>2</v>
+      </c>
+      <c r="L12">
+        <f t="shared" si="7"/>
+        <v>4</v>
+      </c>
+      <c r="M12">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13">
+      <c r="A13" s="17" t="s">
+        <v>92</v>
+      </c>
+      <c r="B13" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v>14B5</v>
+      </c>
+      <c r="C13" s="19" t="s">
+        <v>107</v>
+      </c>
+      <c r="E13">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="F13" t="str">
+        <f t="shared" si="2"/>
+        <v>Super Training</v>
+      </c>
+      <c r="H13">
+        <f t="shared" si="3"/>
+        <v>11</v>
+      </c>
+      <c r="I13" t="str">
+        <f t="shared" si="4"/>
+        <v>B</v>
+      </c>
+      <c r="J13">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="K13">
+        <f t="shared" si="6"/>
+        <v>2</v>
+      </c>
+      <c r="L13">
+        <f t="shared" si="7"/>
+        <v>5</v>
+      </c>
+      <c r="M13">
+        <f t="shared" si="8"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13">
+      <c r="A14" s="17" t="s">
+        <v>93</v>
+      </c>
+      <c r="B14" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v>14B6</v>
+      </c>
+      <c r="C14" s="19" t="s">
+        <v>108</v>
+      </c>
+      <c r="E14">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="F14" t="str">
+        <f t="shared" si="2"/>
+        <v>Move Relearner</v>
+      </c>
+      <c r="H14">
+        <f t="shared" si="3"/>
+        <v>12</v>
+      </c>
+      <c r="I14" t="str">
+        <f t="shared" si="4"/>
+        <v>C</v>
+      </c>
+      <c r="J14">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="K14">
+        <f t="shared" si="6"/>
+        <v>3</v>
+      </c>
+      <c r="L14">
+        <f t="shared" si="7"/>
+        <v>3</v>
+      </c>
+      <c r="M14">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13">
+      <c r="A15" s="17" t="s">
+        <v>94</v>
+      </c>
+      <c r="B15" s="18" t="str">
+        <f t="shared" si="0"/>
+        <v>14B7</v>
+      </c>
+      <c r="C15" s="19" t="s">
+        <v>110</v>
+      </c>
+      <c r="E15">
+        <f t="shared" si="1"/>
+        <v>1</v>
+      </c>
+      <c r="F15" t="str">
+        <f t="shared" si="2"/>
+        <v>Café</v>
+      </c>
+      <c r="H15">
+        <f t="shared" si="3"/>
+        <v>13</v>
+      </c>
+      <c r="I15" t="str">
+        <f t="shared" si="4"/>
+        <v>D</v>
+      </c>
+      <c r="J15">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="K15">
+        <f t="shared" si="6"/>
+        <v>3</v>
+      </c>
+      <c r="L15">
+        <f t="shared" si="7"/>
+        <v>4</v>
+      </c>
+      <c r="M15">
+        <f t="shared" si="8"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" ht="14.6" thickBot="1">
+      <c r="A16" s="20" t="s">
+        <v>95</v>
+      </c>
+      <c r="B16" s="21" t="str">
+        <f t="shared" si="0"/>
+        <v>14B8</v>
+      </c>
+      <c r="C16" s="22" t="s">
+        <v>109</v>
+      </c>
+      <c r="E16">
+        <f t="shared" si="1"/>
+        <v>2</v>
+      </c>
+      <c r="F16" t="str">
+        <f t="shared" si="2"/>
+        <v>Super Training</v>
+      </c>
+      <c r="H16">
+        <f t="shared" si="3"/>
+        <v>14</v>
+      </c>
+      <c r="I16" t="str">
+        <f t="shared" si="4"/>
+        <v>E</v>
+      </c>
+      <c r="J16">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="K16">
+        <f t="shared" si="6"/>
+        <v>3</v>
+      </c>
+      <c r="L16">
+        <f t="shared" si="7"/>
+        <v>5</v>
+      </c>
+      <c r="M16">
+        <f t="shared" si="8"/>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="14.6" thickTop="1"/>
+    <row r="19" spans="1:5">
+      <c r="A19">
+        <v>5655</v>
+      </c>
+      <c r="B19" t="str">
+        <f>DEC2HEX(A19)</f>
+        <v>1617</v>
+      </c>
+      <c r="C19" t="s">
+        <v>114</v>
+      </c>
+      <c r="D19">
+        <v>2</v>
+      </c>
+      <c r="E19">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20">
+        <v>5500</v>
+      </c>
+      <c r="B20" t="str">
+        <f>DEC2HEX(A20)</f>
+        <v>157C</v>
+      </c>
+      <c r="C20" t="s">
+        <v>113</v>
+      </c>
+      <c r="D20">
+        <v>0</v>
+      </c>
+      <c r="E20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="C21" t="s">
+        <v>116</v>
+      </c>
+      <c r="D21">
+        <v>1</v>
+      </c>
+      <c r="E21">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:A16">
+    <sortCondition ref="A2:A16"/>
+  </sortState>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E9BB6F14-E3DE-4AC5-A422-D5C8F6CDB5C6}">
   <dimension ref="A1:I25"/>
   <sheetFormatPr defaultRowHeight="14.15"/>
   <cols>
-    <col min="1" max="1" width="11.5" customWidth="1"/>
-    <col min="2" max="2" width="12.42578125" customWidth="1"/>
+    <col min="1" max="1" width="11.42578125" customWidth="1"/>
+    <col min="2" max="2" width="12.35546875" customWidth="1"/>
     <col min="3" max="3" width="19.78515625" customWidth="1"/>
-    <col min="4" max="4" width="47.28515625" customWidth="1"/>
-    <col min="5" max="5" width="8.92578125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.2109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="47.2109375" customWidth="1"/>
+    <col min="5" max="5" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.140625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="16.5703125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="13.5703125" customWidth="1"/>
-    <col min="10" max="10" width="9.2109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="9.140625" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="16.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="4"/>
-      <c r="I1" s="4"/>
+      <c r="E1" s="2"/>
+      <c r="I1" s="2"/>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="B2" s="4"/>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4"/>
-      <c r="E2" s="4"/>
-      <c r="I2" s="4"/>
+      <c r="A2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="I2" s="2"/>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C3" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -2143,36 +3170,36 @@
         <v>0029A048</v>
       </c>
       <c r="B4" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C4" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
     </row>
     <row r="6" spans="1:9">
-      <c r="A6" s="4" t="s">
-        <v>21</v>
+      <c r="A6" s="2" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="10" spans="1:9">
-      <c r="A10" s="4" t="s">
-        <v>24</v>
+      <c r="A10" s="2" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B11" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C11" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -2181,26 +3208,26 @@
         <v>00341658</v>
       </c>
       <c r="B12" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="C12" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
     </row>
     <row r="17" spans="1:3">
-      <c r="A17" s="4" t="s">
-        <v>23</v>
+      <c r="A17" s="2" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="18" spans="1:3">
       <c r="A18" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="C18" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="19" spans="1:3">
@@ -2209,26 +3236,26 @@
         <v>003417DC</v>
       </c>
       <c r="B19" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="C19" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
     </row>
     <row r="21" spans="1:3">
-      <c r="A21" s="4" t="s">
-        <v>25</v>
+      <c r="A21" s="2" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="22" spans="1:3">
       <c r="A22" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="C22" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -2237,10 +3264,10 @@
         <v>003418C8</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="C23" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -2249,10 +3276,10 @@
         <v>003418CC</v>
       </c>
       <c r="B24" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="C24" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -2261,10 +3288,10 @@
         <v>003418D0</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C25" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
